--- a/artfynd/A 35299-2025 artfynd.xlsx
+++ b/artfynd/A 35299-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104172788</v>
+        <v>104172740</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sydväst om Klammen, Vrm</t>
+          <t>Hagfors, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437081.5579790314</v>
+        <v>437036</v>
       </c>
       <c r="R2" t="n">
-        <v>6667781.670716076</v>
+        <v>6667789</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,12 +771,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -791,12 +786,7 @@
         <v>104173076</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437128.2591591163</v>
+        <v>437129</v>
       </c>
       <c r="R3" t="n">
-        <v>6667798.804257193</v>
+        <v>6667799</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -901,54 +891,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104172740</v>
+        <v>104947414</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hagfors, Vrm</t>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437035.7740560566</v>
+        <v>437101</v>
       </c>
       <c r="R4" t="n">
-        <v>6667788.932489765</v>
+        <v>6667772</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,69 +972,70 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104947414</v>
+        <v>104172788</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+          <t>Sydväst om Klammen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437100.8512489938</v>
+        <v>437082</v>
       </c>
       <c r="R5" t="n">
-        <v>6667771.874558009</v>
+        <v>6667781</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,22 +1059,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,24 +1085,121 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104947305</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>437083</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6667860</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gustav Adolf</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>sälg/asp</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35299-2025 artfynd.xlsx
+++ b/artfynd/A 35299-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104172740</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104173076</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947414</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104172788</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,8 +1225,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947305</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>